--- a/043-01/КДАВ 043-01 Маркровка клемм (4мм) ВЕСЬ КОМПЛЕКТ.xlsx
+++ b/043-01/КДАВ 043-01 Маркровка клемм (4мм) ВЕСЬ КОМПЛЕКТ.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="68">
   <si>
     <t>1</t>
   </si>
@@ -288,10 +288,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -612,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A207"/>
+  <dimension ref="A1:A216"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -921,732 +922,777 @@
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>15</v>
+      <c r="A110" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
-        <v>15</v>
+      <c r="A111" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>16</v>
+      <c r="A112" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>16</v>
+      <c r="A113" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>17</v>
+      <c r="A114" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="2" t="s">
-        <v>31</v>
+      <c r="A131" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>31</v>
+      <c r="A132" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="2" t="s">
-        <v>31</v>
+      <c r="A133" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>65</v>
+      <c r="A137" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>66</v>
+      <c r="A139" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>66</v>
+      <c r="A140" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>67</v>
+      <c r="A141" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="2" t="s">
-        <v>62</v>
+      <c r="A143" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="2" t="s">
-        <v>63</v>
+      <c r="A145" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>63</v>
+      <c r="A146" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="2" t="s">
-        <v>48</v>
+      <c r="A147" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>48</v>
+      <c r="A148" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
-        <v>53</v>
+      <c r="A149" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
-        <v>53</v>
+      <c r="A150" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="2" t="s">
-        <v>25</v>
+      <c r="A178" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="2" t="s">
-        <v>29</v>
+      <c r="A181" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
-        <v>29</v>
+      <c r="A182" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="1" t="s">
-        <v>30</v>
+      <c r="A189" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="2" t="s">
-        <v>33</v>
+      <c r="A191" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" s="2" t="s">
-        <v>34</v>
+      <c r="A199" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" s="1" t="s">
-        <v>20</v>
+      <c r="A200" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" s="2" t="s">
-        <v>20</v>
+      <c r="A201" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202" s="1" t="s">
-        <v>20</v>
+      <c r="A202" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203" s="2" t="s">
-        <v>21</v>
+      <c r="A203" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" s="1" t="s">
-        <v>21</v>
+      <c r="A204" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" s="2" t="s">
-        <v>21</v>
+      <c r="A205" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
         <v>64</v>
       </c>
     </row>
